--- a/backend/products.xlsx
+++ b/backend/products.xlsx
@@ -24,7 +24,7 @@
     <t>Size</t>
   </si>
   <si>
-    <t>Price (৳)</t>
+    <t>sellingPrice</t>
   </si>
   <si>
     <t>Description</t>
@@ -1129,7 +1129,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>12</v>
@@ -1158,7 +1158,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>12</v>
@@ -1187,7 +1187,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>12</v>
@@ -1216,7 +1216,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
@@ -1245,7 +1245,7 @@
         <v>22</v>
       </c>
       <c r="D6" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -1274,7 +1274,7 @@
         <v>23</v>
       </c>
       <c r="D7" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>12</v>
@@ -1303,7 +1303,7 @@
         <v>24</v>
       </c>
       <c r="D8" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
@@ -1332,7 +1332,7 @@
         <v>25</v>
       </c>
       <c r="D9" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>12</v>
@@ -1361,7 +1361,7 @@
         <v>26</v>
       </c>
       <c r="D10" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>12</v>
@@ -1390,7 +1390,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>29</v>
@@ -1651,7 +1651,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>36</v>
@@ -1912,7 +1912,7 @@
         <v>11</v>
       </c>
       <c r="D29" s="2">
-        <v>0.0</v>
+        <v>200.0</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>44</v>
@@ -2173,7 +2173,7 @@
         <v>11</v>
       </c>
       <c r="D38" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>50</v>
@@ -2434,7 +2434,7 @@
         <v>11</v>
       </c>
       <c r="D47" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>56</v>
@@ -2840,7 +2840,7 @@
         <v>11</v>
       </c>
       <c r="D61" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>62</v>
@@ -2956,7 +2956,7 @@
         <v>22</v>
       </c>
       <c r="D65" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>68</v>
@@ -2985,7 +2985,7 @@
         <v>23</v>
       </c>
       <c r="D66" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>68</v>
@@ -3101,7 +3101,7 @@
         <v>11</v>
       </c>
       <c r="D70" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>68</v>
@@ -3130,7 +3130,7 @@
         <v>17</v>
       </c>
       <c r="D71" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>68</v>
@@ -3217,7 +3217,7 @@
         <v>22</v>
       </c>
       <c r="D74" s="2">
-        <v>0.0</v>
+        <v>330.0</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>74</v>
@@ -3246,7 +3246,7 @@
         <v>23</v>
       </c>
       <c r="D75" s="2">
-        <v>0.0</v>
+        <v>780.0</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>74</v>
@@ -3478,7 +3478,7 @@
         <v>22</v>
       </c>
       <c r="D83" s="2">
-        <v>0.0</v>
+        <v>330.0</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>81</v>
@@ -3507,7 +3507,7 @@
         <v>23</v>
       </c>
       <c r="D84" s="2">
-        <v>0.0</v>
+        <v>780.0</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>81</v>
@@ -3623,7 +3623,7 @@
         <v>11</v>
       </c>
       <c r="D88" s="2">
-        <v>0.0</v>
+        <v>180.0</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>81</v>
@@ -3652,7 +3652,7 @@
         <v>17</v>
       </c>
       <c r="D89" s="2">
-        <v>0.0</v>
+        <v>280.0</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>81</v>
@@ -3739,7 +3739,7 @@
         <v>22</v>
       </c>
       <c r="D92" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>87</v>
@@ -3768,7 +3768,7 @@
         <v>23</v>
       </c>
       <c r="D93" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>87</v>
@@ -3797,7 +3797,7 @@
         <v>24</v>
       </c>
       <c r="D94" s="2">
-        <v>0.0</v>
+        <v>1100.0</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>87</v>
@@ -3826,7 +3826,7 @@
         <v>25</v>
       </c>
       <c r="D95" s="2">
-        <v>0.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>87</v>
@@ -3855,7 +3855,7 @@
         <v>26</v>
       </c>
       <c r="D96" s="2">
-        <v>0.0</v>
+        <v>1900.0</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>87</v>
@@ -3884,7 +3884,7 @@
         <v>11</v>
       </c>
       <c r="D97" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>87</v>
@@ -3913,7 +3913,7 @@
         <v>17</v>
       </c>
       <c r="D98" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>87</v>
@@ -3942,7 +3942,7 @@
         <v>18</v>
       </c>
       <c r="D99" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>87</v>
@@ -3971,7 +3971,7 @@
         <v>19</v>
       </c>
       <c r="D100" s="2">
-        <v>0.0</v>
+        <v>1400.0</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>87</v>

--- a/backend/products.xlsx
+++ b/backend/products.xlsx
@@ -814,7 +814,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -832,6 +832,10 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -847,7 +851,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -859,6 +863,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1419,7 +1426,7 @@
         <v>17</v>
       </c>
       <c r="D12" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>29</v>
@@ -1448,7 +1455,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -1477,7 +1484,7 @@
         <v>19</v>
       </c>
       <c r="D14" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>29</v>
@@ -1506,7 +1513,7 @@
         <v>22</v>
       </c>
       <c r="D15" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>29</v>
@@ -1535,7 +1542,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -1564,7 +1571,7 @@
         <v>24</v>
       </c>
       <c r="D17" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>29</v>
@@ -1593,7 +1600,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>29</v>
@@ -1622,7 +1629,7 @@
         <v>26</v>
       </c>
       <c r="D19" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -1680,7 +1687,7 @@
         <v>17</v>
       </c>
       <c r="D21" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>36</v>
@@ -1709,7 +1716,7 @@
         <v>18</v>
       </c>
       <c r="D22" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>36</v>
@@ -1738,7 +1745,7 @@
         <v>19</v>
       </c>
       <c r="D23" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>36</v>
@@ -1767,7 +1774,7 @@
         <v>22</v>
       </c>
       <c r="D24" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>36</v>
@@ -1796,7 +1803,7 @@
         <v>23</v>
       </c>
       <c r="D25" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>36</v>
@@ -1825,7 +1832,7 @@
         <v>24</v>
       </c>
       <c r="D26" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>36</v>
@@ -1854,7 +1861,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>36</v>
@@ -1883,7 +1890,7 @@
         <v>26</v>
       </c>
       <c r="D28" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>36</v>
@@ -1941,7 +1948,7 @@
         <v>17</v>
       </c>
       <c r="D30" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>44</v>
@@ -1970,7 +1977,7 @@
         <v>18</v>
       </c>
       <c r="D31" s="2">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>44</v>
@@ -1999,7 +2006,7 @@
         <v>19</v>
       </c>
       <c r="D32" s="2">
-        <v>0.0</v>
+        <v>1650.0</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>44</v>
@@ -2028,7 +2035,7 @@
         <v>22</v>
       </c>
       <c r="D33" s="2">
-        <v>0.0</v>
+        <v>350.0</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>44</v>
@@ -2057,7 +2064,7 @@
         <v>23</v>
       </c>
       <c r="D34" s="2">
-        <v>0.0</v>
+        <v>850.0</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>44</v>
@@ -2086,7 +2093,7 @@
         <v>24</v>
       </c>
       <c r="D35" s="2">
-        <v>0.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>44</v>
@@ -2115,7 +2122,7 @@
         <v>25</v>
       </c>
       <c r="D36" s="2">
-        <v>0.0</v>
+        <v>1900.0</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>44</v>
@@ -2144,7 +2151,7 @@
         <v>26</v>
       </c>
       <c r="D37" s="2">
-        <v>0.0</v>
+        <v>2200.0</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>44</v>
@@ -2202,7 +2209,7 @@
         <v>17</v>
       </c>
       <c r="D39" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>50</v>
@@ -2231,7 +2238,7 @@
         <v>18</v>
       </c>
       <c r="D40" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>50</v>
@@ -2260,7 +2267,7 @@
         <v>19</v>
       </c>
       <c r="D41" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>50</v>
@@ -2289,7 +2296,7 @@
         <v>22</v>
       </c>
       <c r="D42" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>50</v>
@@ -2318,7 +2325,7 @@
         <v>23</v>
       </c>
       <c r="D43" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>50</v>
@@ -2347,7 +2354,7 @@
         <v>24</v>
       </c>
       <c r="D44" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>50</v>
@@ -2376,7 +2383,7 @@
         <v>25</v>
       </c>
       <c r="D45" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>50</v>
@@ -2405,7 +2412,7 @@
         <v>26</v>
       </c>
       <c r="D46" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>50</v>
@@ -2463,7 +2470,7 @@
         <v>17</v>
       </c>
       <c r="D48" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>56</v>
@@ -2492,7 +2499,7 @@
         <v>18</v>
       </c>
       <c r="D49" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>56</v>
@@ -2521,7 +2528,7 @@
         <v>19</v>
       </c>
       <c r="D50" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>56</v>
@@ -2550,7 +2557,7 @@
         <v>22</v>
       </c>
       <c r="D51" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>56</v>
@@ -2579,7 +2586,7 @@
         <v>23</v>
       </c>
       <c r="D52" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>56</v>
@@ -2608,7 +2615,7 @@
         <v>24</v>
       </c>
       <c r="D53" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>56</v>
@@ -2637,7 +2644,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>56</v>
@@ -2666,7 +2673,7 @@
         <v>26</v>
       </c>
       <c r="D55" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>56</v>
@@ -2695,7 +2702,7 @@
         <v>22</v>
       </c>
       <c r="D56" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>62</v>
@@ -2724,7 +2731,7 @@
         <v>23</v>
       </c>
       <c r="D57" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>62</v>
@@ -2753,7 +2760,7 @@
         <v>24</v>
       </c>
       <c r="D58" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>62</v>
@@ -2782,7 +2789,7 @@
         <v>25</v>
       </c>
       <c r="D59" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>62</v>
@@ -2811,7 +2818,7 @@
         <v>26</v>
       </c>
       <c r="D60" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>62</v>
@@ -2869,7 +2876,7 @@
         <v>17</v>
       </c>
       <c r="D62" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>62</v>
@@ -2898,7 +2905,7 @@
         <v>18</v>
       </c>
       <c r="D63" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>62</v>
@@ -2927,7 +2934,7 @@
         <v>19</v>
       </c>
       <c r="D64" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>62</v>
@@ -3014,7 +3021,7 @@
         <v>24</v>
       </c>
       <c r="D67" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>68</v>
@@ -3043,7 +3050,7 @@
         <v>25</v>
       </c>
       <c r="D68" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>68</v>
@@ -3072,7 +3079,7 @@
         <v>26</v>
       </c>
       <c r="D69" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>68</v>
@@ -3159,7 +3166,7 @@
         <v>18</v>
       </c>
       <c r="D72" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>68</v>
@@ -3188,7 +3195,7 @@
         <v>19</v>
       </c>
       <c r="D73" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>68</v>
@@ -3275,7 +3282,7 @@
         <v>24</v>
       </c>
       <c r="D76" s="2">
-        <v>0.0</v>
+        <v>330.0</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>74</v>
@@ -3304,7 +3311,7 @@
         <v>25</v>
       </c>
       <c r="D77" s="2">
-        <v>0.0</v>
+        <v>780.0</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>74</v>
@@ -3333,7 +3340,7 @@
         <v>26</v>
       </c>
       <c r="D78" s="2">
-        <v>0.0</v>
+        <v>1050.0</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>74</v>
@@ -3362,7 +3369,7 @@
         <v>11</v>
       </c>
       <c r="D79" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>74</v>
@@ -3391,7 +3398,7 @@
         <v>17</v>
       </c>
       <c r="D80" s="2">
-        <v>0.0</v>
+        <v>1650.0</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>74</v>
@@ -3420,7 +3427,7 @@
         <v>18</v>
       </c>
       <c r="D81" s="2">
-        <v>0.0</v>
+        <v>180.0</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>74</v>
@@ -3449,7 +3456,7 @@
         <v>19</v>
       </c>
       <c r="D82" s="2">
-        <v>0.0</v>
+        <v>280.0</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>74</v>
@@ -3478,7 +3485,7 @@
         <v>22</v>
       </c>
       <c r="D83" s="2">
-        <v>330.0</v>
+        <v>750.0</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>81</v>
@@ -3507,7 +3514,7 @@
         <v>23</v>
       </c>
       <c r="D84" s="2">
-        <v>780.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>81</v>
@@ -3536,7 +3543,7 @@
         <v>24</v>
       </c>
       <c r="D85" s="2">
-        <v>0.0</v>
+        <v>1050.0</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>81</v>
@@ -3565,7 +3572,7 @@
         <v>25</v>
       </c>
       <c r="D86" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>81</v>
@@ -3594,7 +3601,7 @@
         <v>26</v>
       </c>
       <c r="D87" s="2">
-        <v>0.0</v>
+        <v>1650.0</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>81</v>
@@ -3681,7 +3688,7 @@
         <v>18</v>
       </c>
       <c r="D90" s="2">
-        <v>0.0</v>
+        <v>750.0</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>81</v>
@@ -3710,7 +3717,7 @@
         <v>19</v>
       </c>
       <c r="D91" s="2">
-        <v>0.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>81</v>
@@ -4000,7 +4007,7 @@
         <v>22</v>
       </c>
       <c r="D101" s="2">
-        <v>0.0</v>
+        <v>330.0</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>92</v>
@@ -4029,7 +4036,7 @@
         <v>23</v>
       </c>
       <c r="D102" s="2">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>92</v>
@@ -4058,7 +4065,7 @@
         <v>24</v>
       </c>
       <c r="D103" s="2">
-        <v>0.0</v>
+        <v>1100.0</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>92</v>
@@ -4087,7 +4094,7 @@
         <v>25</v>
       </c>
       <c r="D104" s="2">
-        <v>0.0</v>
+        <v>1400.0</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>92</v>
@@ -4116,7 +4123,7 @@
         <v>26</v>
       </c>
       <c r="D105" s="2">
-        <v>0.0</v>
+        <v>1800.0</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>92</v>
@@ -4145,7 +4152,7 @@
         <v>11</v>
       </c>
       <c r="D106" s="2">
-        <v>0.0</v>
+        <v>180.0</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>92</v>
@@ -4174,7 +4181,7 @@
         <v>17</v>
       </c>
       <c r="D107" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>92</v>
@@ -4203,7 +4210,7 @@
         <v>18</v>
       </c>
       <c r="D108" s="2">
-        <v>0.0</v>
+        <v>750.0</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>92</v>
@@ -4232,7 +4239,7 @@
         <v>19</v>
       </c>
       <c r="D109" s="2">
-        <v>0.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>92</v>
@@ -4261,7 +4268,7 @@
         <v>22</v>
       </c>
       <c r="D110" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>98</v>
@@ -4290,7 +4297,7 @@
         <v>23</v>
       </c>
       <c r="D111" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>98</v>
@@ -4319,7 +4326,7 @@
         <v>24</v>
       </c>
       <c r="D112" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>98</v>
@@ -4348,7 +4355,7 @@
         <v>25</v>
       </c>
       <c r="D113" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>98</v>
@@ -4377,7 +4384,7 @@
         <v>26</v>
       </c>
       <c r="D114" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>98</v>
@@ -4406,7 +4413,7 @@
         <v>11</v>
       </c>
       <c r="D115" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>98</v>
@@ -4435,7 +4442,7 @@
         <v>17</v>
       </c>
       <c r="D116" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>98</v>
@@ -4464,7 +4471,7 @@
         <v>18</v>
       </c>
       <c r="D117" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>98</v>
@@ -4493,7 +4500,7 @@
         <v>19</v>
       </c>
       <c r="D118" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>98</v>
@@ -4522,7 +4529,7 @@
         <v>22</v>
       </c>
       <c r="D119" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>104</v>
@@ -4551,7 +4558,7 @@
         <v>23</v>
       </c>
       <c r="D120" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>104</v>
@@ -4580,7 +4587,7 @@
         <v>24</v>
       </c>
       <c r="D121" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>104</v>
@@ -4609,7 +4616,7 @@
         <v>25</v>
       </c>
       <c r="D122" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>104</v>
@@ -4638,7 +4645,7 @@
         <v>26</v>
       </c>
       <c r="D123" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>104</v>
@@ -4667,7 +4674,7 @@
         <v>11</v>
       </c>
       <c r="D124" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>104</v>
@@ -4696,7 +4703,7 @@
         <v>17</v>
       </c>
       <c r="D125" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>104</v>
@@ -4725,7 +4732,7 @@
         <v>18</v>
       </c>
       <c r="D126" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>104</v>
@@ -4754,7 +4761,7 @@
         <v>19</v>
       </c>
       <c r="D127" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>104</v>
@@ -4782,8 +4789,8 @@
       <c r="C128" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D128" s="2">
-        <v>0.0</v>
+      <c r="D128" s="4">
+        <v>330.0</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>109</v>
@@ -4811,8 +4818,8 @@
       <c r="C129" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D129" s="2">
-        <v>0.0</v>
+      <c r="D129" s="4">
+        <v>780.0</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>109</v>
@@ -4840,8 +4847,8 @@
       <c r="C130" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D130" s="2">
-        <v>0.0</v>
+      <c r="D130" s="4">
+        <v>1050.0</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>109</v>
@@ -4869,8 +4876,8 @@
       <c r="C131" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="2">
-        <v>0.0</v>
+      <c r="D131" s="4">
+        <v>1300.0</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>109</v>
@@ -4898,8 +4905,8 @@
       <c r="C132" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D132" s="2">
-        <v>0.0</v>
+      <c r="D132" s="4">
+        <v>1650.0</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>109</v>
@@ -4927,8 +4934,8 @@
       <c r="C133" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D133" s="2">
-        <v>0.0</v>
+      <c r="D133" s="4">
+        <v>180.0</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>109</v>
@@ -4956,8 +4963,8 @@
       <c r="C134" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D134" s="2">
-        <v>0.0</v>
+      <c r="D134" s="4">
+        <v>280.0</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>109</v>
@@ -4985,8 +4992,8 @@
       <c r="C135" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D135" s="2">
-        <v>0.0</v>
+      <c r="D135" s="4">
+        <v>750.0</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>109</v>
@@ -5014,8 +5021,8 @@
       <c r="C136" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D136" s="2">
-        <v>0.0</v>
+      <c r="D136" s="4">
+        <v>1500.0</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>109</v>
@@ -5044,7 +5051,7 @@
         <v>22</v>
       </c>
       <c r="D137" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>115</v>
@@ -5073,7 +5080,7 @@
         <v>23</v>
       </c>
       <c r="D138" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>115</v>
@@ -5102,7 +5109,7 @@
         <v>24</v>
       </c>
       <c r="D139" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>115</v>
@@ -5131,7 +5138,7 @@
         <v>25</v>
       </c>
       <c r="D140" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>115</v>
@@ -5160,7 +5167,7 @@
         <v>26</v>
       </c>
       <c r="D141" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>115</v>
@@ -5189,7 +5196,7 @@
         <v>11</v>
       </c>
       <c r="D142" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>115</v>
@@ -5218,7 +5225,7 @@
         <v>17</v>
       </c>
       <c r="D143" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>115</v>
@@ -5247,7 +5254,7 @@
         <v>18</v>
       </c>
       <c r="D144" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>115</v>
@@ -5276,7 +5283,7 @@
         <v>19</v>
       </c>
       <c r="D145" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>115</v>
@@ -5305,7 +5312,7 @@
         <v>22</v>
       </c>
       <c r="D146" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>121</v>
@@ -5334,7 +5341,7 @@
         <v>23</v>
       </c>
       <c r="D147" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>121</v>
@@ -5363,7 +5370,7 @@
         <v>24</v>
       </c>
       <c r="D148" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>121</v>
@@ -5392,7 +5399,7 @@
         <v>25</v>
       </c>
       <c r="D149" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>121</v>
@@ -5421,7 +5428,7 @@
         <v>26</v>
       </c>
       <c r="D150" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>121</v>
@@ -5450,7 +5457,7 @@
         <v>11</v>
       </c>
       <c r="D151" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>121</v>
@@ -5479,7 +5486,7 @@
         <v>17</v>
       </c>
       <c r="D152" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>121</v>
@@ -5508,7 +5515,7 @@
         <v>18</v>
       </c>
       <c r="D153" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>121</v>
@@ -5537,7 +5544,7 @@
         <v>19</v>
       </c>
       <c r="D154" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>121</v>
@@ -5566,7 +5573,7 @@
         <v>22</v>
       </c>
       <c r="D155" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>128</v>
@@ -5595,7 +5602,7 @@
         <v>23</v>
       </c>
       <c r="D156" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>128</v>
@@ -5624,7 +5631,7 @@
         <v>24</v>
       </c>
       <c r="D157" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>128</v>
@@ -5653,7 +5660,7 @@
         <v>25</v>
       </c>
       <c r="D158" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>128</v>
@@ -5682,7 +5689,7 @@
         <v>26</v>
       </c>
       <c r="D159" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>128</v>
@@ -5711,7 +5718,7 @@
         <v>11</v>
       </c>
       <c r="D160" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>128</v>
@@ -5740,7 +5747,7 @@
         <v>17</v>
       </c>
       <c r="D161" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>128</v>
@@ -5769,7 +5776,7 @@
         <v>18</v>
       </c>
       <c r="D162" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>128</v>
@@ -5798,7 +5805,7 @@
         <v>19</v>
       </c>
       <c r="D163" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>128</v>
@@ -5827,7 +5834,7 @@
         <v>22</v>
       </c>
       <c r="D164" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>134</v>
@@ -5856,7 +5863,7 @@
         <v>23</v>
       </c>
       <c r="D165" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>134</v>
@@ -5885,7 +5892,7 @@
         <v>24</v>
       </c>
       <c r="D166" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>134</v>
@@ -5914,7 +5921,7 @@
         <v>25</v>
       </c>
       <c r="D167" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>134</v>
@@ -5943,7 +5950,7 @@
         <v>26</v>
       </c>
       <c r="D168" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>134</v>
@@ -5972,7 +5979,7 @@
         <v>11</v>
       </c>
       <c r="D169" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>134</v>
@@ -6001,7 +6008,7 @@
         <v>17</v>
       </c>
       <c r="D170" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>134</v>
@@ -6030,7 +6037,7 @@
         <v>18</v>
       </c>
       <c r="D171" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>134</v>
@@ -6059,7 +6066,7 @@
         <v>19</v>
       </c>
       <c r="D172" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>134</v>
@@ -6087,8 +6094,8 @@
       <c r="C173" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D173" s="2">
-        <v>0.0</v>
+      <c r="D173" s="4">
+        <v>330.0</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>140</v>
@@ -6116,8 +6123,8 @@
       <c r="C174" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D174" s="2">
-        <v>0.0</v>
+      <c r="D174" s="4">
+        <v>780.0</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>140</v>
@@ -6145,8 +6152,8 @@
       <c r="C175" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D175" s="2">
-        <v>0.0</v>
+      <c r="D175" s="4">
+        <v>1050.0</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>140</v>
@@ -6174,8 +6181,8 @@
       <c r="C176" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D176" s="2">
-        <v>0.0</v>
+      <c r="D176" s="4">
+        <v>1300.0</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>140</v>
@@ -6203,8 +6210,8 @@
       <c r="C177" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D177" s="2">
-        <v>0.0</v>
+      <c r="D177" s="4">
+        <v>1650.0</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>140</v>
@@ -6232,8 +6239,8 @@
       <c r="C178" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D178" s="2">
-        <v>0.0</v>
+      <c r="D178" s="4">
+        <v>180.0</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>140</v>
@@ -6261,8 +6268,8 @@
       <c r="C179" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D179" s="2">
-        <v>0.0</v>
+      <c r="D179" s="4">
+        <v>280.0</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>140</v>
@@ -6290,8 +6297,8 @@
       <c r="C180" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D180" s="2">
-        <v>0.0</v>
+      <c r="D180" s="4">
+        <v>750.0</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>140</v>
@@ -6319,8 +6326,8 @@
       <c r="C181" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D181" s="2">
-        <v>0.0</v>
+      <c r="D181" s="4">
+        <v>1500.0</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>140</v>
@@ -6348,8 +6355,8 @@
       <c r="C182" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D182" s="2">
-        <v>0.0</v>
+      <c r="D182" s="4">
+        <v>330.0</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>147</v>
@@ -6377,8 +6384,8 @@
       <c r="C183" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D183" s="2">
-        <v>0.0</v>
+      <c r="D183" s="4">
+        <v>780.0</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>147</v>
@@ -6406,8 +6413,8 @@
       <c r="C184" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D184" s="2">
-        <v>0.0</v>
+      <c r="D184" s="4">
+        <v>1050.0</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>147</v>
@@ -6435,8 +6442,8 @@
       <c r="C185" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D185" s="2">
-        <v>0.0</v>
+      <c r="D185" s="4">
+        <v>1300.0</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>147</v>
@@ -6464,8 +6471,8 @@
       <c r="C186" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D186" s="2">
-        <v>0.0</v>
+      <c r="D186" s="4">
+        <v>1650.0</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>147</v>
@@ -6493,8 +6500,8 @@
       <c r="C187" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D187" s="2">
-        <v>0.0</v>
+      <c r="D187" s="4">
+        <v>180.0</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>147</v>
@@ -6522,8 +6529,8 @@
       <c r="C188" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D188" s="2">
-        <v>0.0</v>
+      <c r="D188" s="4">
+        <v>280.0</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>147</v>
@@ -6551,8 +6558,8 @@
       <c r="C189" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D189" s="2">
-        <v>0.0</v>
+      <c r="D189" s="4">
+        <v>750.0</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>147</v>
@@ -6580,8 +6587,8 @@
       <c r="C190" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D190" s="2">
-        <v>0.0</v>
+      <c r="D190" s="4">
+        <v>1500.0</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>147</v>
@@ -6610,7 +6617,7 @@
         <v>22</v>
       </c>
       <c r="D191" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>153</v>
@@ -6639,7 +6646,7 @@
         <v>23</v>
       </c>
       <c r="D192" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>153</v>
@@ -6668,7 +6675,7 @@
         <v>24</v>
       </c>
       <c r="D193" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>153</v>
@@ -6697,7 +6704,7 @@
         <v>25</v>
       </c>
       <c r="D194" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>153</v>
@@ -6726,7 +6733,7 @@
         <v>26</v>
       </c>
       <c r="D195" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>153</v>
@@ -6755,7 +6762,7 @@
         <v>11</v>
       </c>
       <c r="D196" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>153</v>
@@ -6784,7 +6791,7 @@
         <v>17</v>
       </c>
       <c r="D197" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>153</v>
@@ -6813,7 +6820,7 @@
         <v>18</v>
       </c>
       <c r="D198" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>153</v>
@@ -6842,7 +6849,7 @@
         <v>19</v>
       </c>
       <c r="D199" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>153</v>
@@ -6871,7 +6878,7 @@
         <v>22</v>
       </c>
       <c r="D200" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>159</v>
@@ -6900,7 +6907,7 @@
         <v>23</v>
       </c>
       <c r="D201" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>159</v>
@@ -6929,7 +6936,7 @@
         <v>24</v>
       </c>
       <c r="D202" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>159</v>
@@ -6958,7 +6965,7 @@
         <v>25</v>
       </c>
       <c r="D203" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>159</v>
@@ -6987,7 +6994,7 @@
         <v>26</v>
       </c>
       <c r="D204" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>159</v>
@@ -7016,7 +7023,7 @@
         <v>11</v>
       </c>
       <c r="D205" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>159</v>
@@ -7045,7 +7052,7 @@
         <v>17</v>
       </c>
       <c r="D206" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>159</v>
@@ -7074,7 +7081,7 @@
         <v>18</v>
       </c>
       <c r="D207" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>159</v>
@@ -7103,7 +7110,7 @@
         <v>19</v>
       </c>
       <c r="D208" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>159</v>
@@ -7131,8 +7138,8 @@
       <c r="C209" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D209" s="2">
-        <v>0.0</v>
+      <c r="D209" s="4">
+        <v>330.0</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>164</v>
@@ -7160,8 +7167,8 @@
       <c r="C210" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D210" s="2">
-        <v>0.0</v>
+      <c r="D210" s="4">
+        <v>780.0</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>164</v>
@@ -7189,8 +7196,8 @@
       <c r="C211" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D211" s="2">
-        <v>0.0</v>
+      <c r="D211" s="4">
+        <v>1050.0</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>164</v>
@@ -7218,8 +7225,8 @@
       <c r="C212" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D212" s="2">
-        <v>0.0</v>
+      <c r="D212" s="4">
+        <v>1300.0</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>164</v>
@@ -7247,8 +7254,8 @@
       <c r="C213" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D213" s="2">
-        <v>0.0</v>
+      <c r="D213" s="4">
+        <v>1650.0</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>164</v>
@@ -7276,8 +7283,8 @@
       <c r="C214" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D214" s="2">
-        <v>0.0</v>
+      <c r="D214" s="4">
+        <v>180.0</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>164</v>
@@ -7305,8 +7312,8 @@
       <c r="C215" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D215" s="2">
-        <v>0.0</v>
+      <c r="D215" s="4">
+        <v>280.0</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>164</v>
@@ -7334,8 +7341,8 @@
       <c r="C216" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D216" s="2">
-        <v>0.0</v>
+      <c r="D216" s="4">
+        <v>750.0</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>164</v>
@@ -7363,8 +7370,8 @@
       <c r="C217" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D217" s="2">
-        <v>0.0</v>
+      <c r="D217" s="4">
+        <v>1500.0</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>164</v>
@@ -7393,7 +7400,7 @@
         <v>22</v>
       </c>
       <c r="D218" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>170</v>
@@ -7422,7 +7429,7 @@
         <v>23</v>
       </c>
       <c r="D219" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>170</v>
@@ -7451,7 +7458,7 @@
         <v>24</v>
       </c>
       <c r="D220" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>170</v>
@@ -7480,7 +7487,7 @@
         <v>25</v>
       </c>
       <c r="D221" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>170</v>
@@ -7509,7 +7516,7 @@
         <v>26</v>
       </c>
       <c r="D222" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>170</v>
@@ -7538,7 +7545,7 @@
         <v>11</v>
       </c>
       <c r="D223" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>170</v>
@@ -7567,7 +7574,7 @@
         <v>17</v>
       </c>
       <c r="D224" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>170</v>
@@ -7596,7 +7603,7 @@
         <v>18</v>
       </c>
       <c r="D225" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>170</v>
@@ -7625,7 +7632,7 @@
         <v>19</v>
       </c>
       <c r="D226" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>170</v>
@@ -7653,8 +7660,8 @@
       <c r="C227" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D227" s="2">
-        <v>0.0</v>
+      <c r="D227" s="4">
+        <v>330.0</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>176</v>
@@ -7682,8 +7689,8 @@
       <c r="C228" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D228" s="2">
-        <v>0.0</v>
+      <c r="D228" s="4">
+        <v>780.0</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>176</v>
@@ -7711,8 +7718,8 @@
       <c r="C229" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D229" s="2">
-        <v>0.0</v>
+      <c r="D229" s="4">
+        <v>1050.0</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>176</v>
@@ -7740,8 +7747,8 @@
       <c r="C230" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D230" s="2">
-        <v>0.0</v>
+      <c r="D230" s="4">
+        <v>1300.0</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>176</v>
@@ -7769,8 +7776,8 @@
       <c r="C231" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D231" s="2">
-        <v>0.0</v>
+      <c r="D231" s="4">
+        <v>1650.0</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>176</v>
@@ -7798,8 +7805,8 @@
       <c r="C232" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D232" s="2">
-        <v>0.0</v>
+      <c r="D232" s="4">
+        <v>180.0</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>176</v>
@@ -7827,8 +7834,8 @@
       <c r="C233" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D233" s="2">
-        <v>0.0</v>
+      <c r="D233" s="4">
+        <v>280.0</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>176</v>
@@ -7856,8 +7863,8 @@
       <c r="C234" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D234" s="2">
-        <v>0.0</v>
+      <c r="D234" s="4">
+        <v>750.0</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>176</v>
@@ -7885,8 +7892,8 @@
       <c r="C235" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D235" s="2">
-        <v>0.0</v>
+      <c r="D235" s="4">
+        <v>1500.0</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>176</v>
@@ -7915,7 +7922,7 @@
         <v>22</v>
       </c>
       <c r="D236" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>182</v>
@@ -7944,7 +7951,7 @@
         <v>23</v>
       </c>
       <c r="D237" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>182</v>
@@ -7973,7 +7980,7 @@
         <v>24</v>
       </c>
       <c r="D238" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>182</v>
@@ -8002,7 +8009,7 @@
         <v>25</v>
       </c>
       <c r="D239" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>182</v>
@@ -8031,7 +8038,7 @@
         <v>26</v>
       </c>
       <c r="D240" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>182</v>
@@ -8060,7 +8067,7 @@
         <v>11</v>
       </c>
       <c r="D241" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>182</v>
@@ -8089,7 +8096,7 @@
         <v>17</v>
       </c>
       <c r="D242" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>182</v>
@@ -8118,7 +8125,7 @@
         <v>18</v>
       </c>
       <c r="D243" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>182</v>
@@ -8147,7 +8154,7 @@
         <v>19</v>
       </c>
       <c r="D244" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>182</v>
@@ -8175,8 +8182,8 @@
       <c r="C245" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D245" s="2">
-        <v>0.0</v>
+      <c r="D245" s="4">
+        <v>330.0</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>188</v>
@@ -8204,8 +8211,8 @@
       <c r="C246" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D246" s="2">
-        <v>0.0</v>
+      <c r="D246" s="4">
+        <v>780.0</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>188</v>
@@ -8233,8 +8240,8 @@
       <c r="C247" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D247" s="2">
-        <v>0.0</v>
+      <c r="D247" s="4">
+        <v>1050.0</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>188</v>
@@ -8262,8 +8269,8 @@
       <c r="C248" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D248" s="2">
-        <v>0.0</v>
+      <c r="D248" s="4">
+        <v>1300.0</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>188</v>
@@ -8291,8 +8298,8 @@
       <c r="C249" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D249" s="2">
-        <v>0.0</v>
+      <c r="D249" s="4">
+        <v>1650.0</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>188</v>
@@ -8320,8 +8327,8 @@
       <c r="C250" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D250" s="2">
-        <v>0.0</v>
+      <c r="D250" s="4">
+        <v>180.0</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>188</v>
@@ -8349,8 +8356,8 @@
       <c r="C251" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D251" s="2">
-        <v>0.0</v>
+      <c r="D251" s="4">
+        <v>280.0</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>188</v>
@@ -8378,8 +8385,8 @@
       <c r="C252" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D252" s="2">
-        <v>0.0</v>
+      <c r="D252" s="4">
+        <v>750.0</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>188</v>
@@ -8407,8 +8414,8 @@
       <c r="C253" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D253" s="2">
-        <v>0.0</v>
+      <c r="D253" s="4">
+        <v>1500.0</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>188</v>
@@ -8436,8 +8443,8 @@
       <c r="C254" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D254" s="2">
-        <v>0.0</v>
+      <c r="D254" s="4">
+        <v>330.0</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>193</v>
@@ -8465,8 +8472,8 @@
       <c r="C255" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D255" s="2">
-        <v>0.0</v>
+      <c r="D255" s="4">
+        <v>780.0</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>193</v>
@@ -8494,8 +8501,8 @@
       <c r="C256" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D256" s="2">
-        <v>0.0</v>
+      <c r="D256" s="4">
+        <v>1050.0</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>193</v>
@@ -8523,8 +8530,8 @@
       <c r="C257" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D257" s="2">
-        <v>0.0</v>
+      <c r="D257" s="4">
+        <v>1300.0</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>193</v>
@@ -8552,8 +8559,8 @@
       <c r="C258" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D258" s="2">
-        <v>0.0</v>
+      <c r="D258" s="4">
+        <v>1650.0</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>193</v>
@@ -8581,8 +8588,8 @@
       <c r="C259" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D259" s="2">
-        <v>0.0</v>
+      <c r="D259" s="4">
+        <v>180.0</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>193</v>
@@ -8610,8 +8617,8 @@
       <c r="C260" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D260" s="2">
-        <v>0.0</v>
+      <c r="D260" s="4">
+        <v>280.0</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>193</v>
@@ -8639,8 +8646,8 @@
       <c r="C261" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D261" s="2">
-        <v>0.0</v>
+      <c r="D261" s="4">
+        <v>750.0</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>193</v>
@@ -8668,8 +8675,8 @@
       <c r="C262" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D262" s="2">
-        <v>0.0</v>
+      <c r="D262" s="4">
+        <v>1500.0</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>193</v>
@@ -8697,8 +8704,8 @@
       <c r="C263" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D263" s="2">
-        <v>0.0</v>
+      <c r="D263" s="4">
+        <v>330.0</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>199</v>
@@ -8726,8 +8733,8 @@
       <c r="C264" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D264" s="2">
-        <v>0.0</v>
+      <c r="D264" s="4">
+        <v>780.0</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>199</v>
@@ -8755,8 +8762,8 @@
       <c r="C265" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D265" s="2">
-        <v>0.0</v>
+      <c r="D265" s="4">
+        <v>1050.0</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>199</v>
@@ -8784,8 +8791,8 @@
       <c r="C266" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D266" s="2">
-        <v>0.0</v>
+      <c r="D266" s="4">
+        <v>1300.0</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>199</v>
@@ -8813,8 +8820,8 @@
       <c r="C267" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D267" s="2">
-        <v>0.0</v>
+      <c r="D267" s="4">
+        <v>1650.0</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>199</v>
@@ -8842,8 +8849,8 @@
       <c r="C268" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D268" s="2">
-        <v>0.0</v>
+      <c r="D268" s="4">
+        <v>180.0</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>199</v>
@@ -8871,8 +8878,8 @@
       <c r="C269" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D269" s="2">
-        <v>0.0</v>
+      <c r="D269" s="4">
+        <v>280.0</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>199</v>
@@ -8900,8 +8907,8 @@
       <c r="C270" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D270" s="2">
-        <v>0.0</v>
+      <c r="D270" s="4">
+        <v>750.0</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>199</v>
@@ -8929,8 +8936,8 @@
       <c r="C271" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D271" s="2">
-        <v>0.0</v>
+      <c r="D271" s="4">
+        <v>1500.0</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>199</v>
@@ -8958,8 +8965,8 @@
       <c r="C272" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D272" s="2">
-        <v>0.0</v>
+      <c r="D272" s="4">
+        <v>330.0</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>205</v>
@@ -8987,8 +8994,8 @@
       <c r="C273" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D273" s="2">
-        <v>0.0</v>
+      <c r="D273" s="4">
+        <v>780.0</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>205</v>
@@ -9016,8 +9023,8 @@
       <c r="C274" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D274" s="2">
-        <v>0.0</v>
+      <c r="D274" s="4">
+        <v>1050.0</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>205</v>
@@ -9045,8 +9052,8 @@
       <c r="C275" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D275" s="2">
-        <v>0.0</v>
+      <c r="D275" s="4">
+        <v>1300.0</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>205</v>
@@ -9074,8 +9081,8 @@
       <c r="C276" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D276" s="2">
-        <v>0.0</v>
+      <c r="D276" s="4">
+        <v>1650.0</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>205</v>
@@ -9103,8 +9110,8 @@
       <c r="C277" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D277" s="2">
-        <v>0.0</v>
+      <c r="D277" s="4">
+        <v>180.0</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>205</v>
@@ -9132,8 +9139,8 @@
       <c r="C278" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D278" s="2">
-        <v>0.0</v>
+      <c r="D278" s="4">
+        <v>280.0</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>205</v>
@@ -9161,8 +9168,8 @@
       <c r="C279" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D279" s="2">
-        <v>0.0</v>
+      <c r="D279" s="4">
+        <v>750.0</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>205</v>
@@ -9190,8 +9197,8 @@
       <c r="C280" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D280" s="2">
-        <v>0.0</v>
+      <c r="D280" s="4">
+        <v>1500.0</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>205</v>
@@ -9219,8 +9226,8 @@
       <c r="C281" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D281" s="2">
-        <v>0.0</v>
+      <c r="D281" s="4">
+        <v>330.0</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>210</v>
@@ -9248,8 +9255,8 @@
       <c r="C282" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D282" s="2">
-        <v>0.0</v>
+      <c r="D282" s="4">
+        <v>780.0</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>210</v>
@@ -9277,8 +9284,8 @@
       <c r="C283" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D283" s="2">
-        <v>0.0</v>
+      <c r="D283" s="4">
+        <v>1050.0</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>210</v>
@@ -9306,8 +9313,8 @@
       <c r="C284" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D284" s="2">
-        <v>0.0</v>
+      <c r="D284" s="4">
+        <v>1300.0</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>210</v>
@@ -9335,8 +9342,8 @@
       <c r="C285" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D285" s="2">
-        <v>0.0</v>
+      <c r="D285" s="4">
+        <v>1650.0</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>210</v>
@@ -9364,8 +9371,8 @@
       <c r="C286" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D286" s="2">
-        <v>0.0</v>
+      <c r="D286" s="4">
+        <v>180.0</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>210</v>
@@ -9393,8 +9400,8 @@
       <c r="C287" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D287" s="2">
-        <v>0.0</v>
+      <c r="D287" s="4">
+        <v>280.0</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>210</v>
@@ -9422,8 +9429,8 @@
       <c r="C288" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D288" s="2">
-        <v>0.0</v>
+      <c r="D288" s="4">
+        <v>750.0</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>210</v>
@@ -9451,8 +9458,8 @@
       <c r="C289" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D289" s="2">
-        <v>0.0</v>
+      <c r="D289" s="4">
+        <v>1500.0</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>210</v>
@@ -9481,7 +9488,7 @@
         <v>22</v>
       </c>
       <c r="D290" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>215</v>
@@ -9510,7 +9517,7 @@
         <v>23</v>
       </c>
       <c r="D291" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>215</v>
@@ -9539,7 +9546,7 @@
         <v>24</v>
       </c>
       <c r="D292" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>215</v>
@@ -9568,7 +9575,7 @@
         <v>25</v>
       </c>
       <c r="D293" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>215</v>
@@ -9597,7 +9604,7 @@
         <v>26</v>
       </c>
       <c r="D294" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>215</v>
@@ -9626,7 +9633,7 @@
         <v>11</v>
       </c>
       <c r="D295" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>215</v>
@@ -9655,7 +9662,7 @@
         <v>17</v>
       </c>
       <c r="D296" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>215</v>
@@ -9684,7 +9691,7 @@
         <v>18</v>
       </c>
       <c r="D297" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>215</v>
@@ -9713,7 +9720,7 @@
         <v>19</v>
       </c>
       <c r="D298" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>215</v>
@@ -9742,7 +9749,7 @@
         <v>22</v>
       </c>
       <c r="D299" s="2">
-        <v>0.0</v>
+        <v>350.0</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>220</v>
@@ -9771,7 +9778,7 @@
         <v>23</v>
       </c>
       <c r="D300" s="2">
-        <v>0.0</v>
+        <v>850.0</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>220</v>
@@ -9800,7 +9807,7 @@
         <v>24</v>
       </c>
       <c r="D301" s="2">
-        <v>0.0</v>
+        <v>1550.0</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>220</v>
@@ -9829,7 +9836,7 @@
         <v>25</v>
       </c>
       <c r="D302" s="2">
-        <v>0.0</v>
+        <v>1850.0</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>220</v>
@@ -9858,7 +9865,7 @@
         <v>26</v>
       </c>
       <c r="D303" s="2">
-        <v>0.0</v>
+        <v>2200.0</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>220</v>
@@ -9887,7 +9894,7 @@
         <v>11</v>
       </c>
       <c r="D304" s="2">
-        <v>0.0</v>
+        <v>200.0</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>220</v>
@@ -9916,7 +9923,7 @@
         <v>17</v>
       </c>
       <c r="D305" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>220</v>
@@ -9945,7 +9952,7 @@
         <v>18</v>
       </c>
       <c r="D306" s="2">
-        <v>0.0</v>
+        <v>750.0</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>220</v>
@@ -9974,7 +9981,7 @@
         <v>19</v>
       </c>
       <c r="D307" s="2">
-        <v>0.0</v>
+        <v>1450.0</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>220</v>
@@ -10003,7 +10010,7 @@
         <v>22</v>
       </c>
       <c r="D308" s="2">
-        <v>0.0</v>
+        <v>350.0</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>226</v>
@@ -10032,7 +10039,7 @@
         <v>23</v>
       </c>
       <c r="D309" s="2">
-        <v>0.0</v>
+        <v>850.0</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>226</v>
@@ -10061,7 +10068,7 @@
         <v>24</v>
       </c>
       <c r="D310" s="2">
-        <v>0.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>226</v>
@@ -10090,7 +10097,7 @@
         <v>25</v>
       </c>
       <c r="D311" s="2">
-        <v>0.0</v>
+        <v>1900.0</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>226</v>
@@ -10119,7 +10126,7 @@
         <v>26</v>
       </c>
       <c r="D312" s="2">
-        <v>0.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>226</v>
@@ -10148,7 +10155,7 @@
         <v>11</v>
       </c>
       <c r="D313" s="2">
-        <v>0.0</v>
+        <v>200.0</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>226</v>
@@ -10177,7 +10184,7 @@
         <v>17</v>
       </c>
       <c r="D314" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>226</v>
@@ -10206,7 +10213,7 @@
         <v>18</v>
       </c>
       <c r="D315" s="2">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>226</v>
@@ -10235,7 +10242,7 @@
         <v>19</v>
       </c>
       <c r="D316" s="2">
-        <v>0.0</v>
+        <v>1450.0</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>226</v>
@@ -10264,7 +10271,7 @@
         <v>22</v>
       </c>
       <c r="D317" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>231</v>
@@ -10293,7 +10300,7 @@
         <v>23</v>
       </c>
       <c r="D318" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>231</v>
@@ -10322,7 +10329,7 @@
         <v>24</v>
       </c>
       <c r="D319" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>231</v>
@@ -10351,7 +10358,7 @@
         <v>25</v>
       </c>
       <c r="D320" s="2">
-        <v>0.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>231</v>
@@ -10380,7 +10387,7 @@
         <v>26</v>
       </c>
       <c r="D321" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>231</v>
@@ -10409,7 +10416,7 @@
         <v>11</v>
       </c>
       <c r="D322" s="2">
-        <v>0.0</v>
+        <v>150.0</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>231</v>
@@ -10438,7 +10445,7 @@
         <v>17</v>
       </c>
       <c r="D323" s="2">
-        <v>0.0</v>
+        <v>250.0</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>231</v>
@@ -10467,7 +10474,7 @@
         <v>18</v>
       </c>
       <c r="D324" s="2">
-        <v>0.0</v>
+        <v>650.0</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>231</v>
@@ -10496,7 +10503,7 @@
         <v>19</v>
       </c>
       <c r="D325" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>231</v>
@@ -10525,7 +10532,7 @@
         <v>22</v>
       </c>
       <c r="D326" s="2">
-        <v>0.0</v>
+        <v>330.0</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>237</v>
@@ -10554,7 +10561,7 @@
         <v>23</v>
       </c>
       <c r="D327" s="2">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>237</v>
@@ -10583,7 +10590,7 @@
         <v>24</v>
       </c>
       <c r="D328" s="2">
-        <v>0.0</v>
+        <v>1400.0</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>237</v>
@@ -10612,7 +10619,7 @@
         <v>25</v>
       </c>
       <c r="D329" s="2">
-        <v>0.0</v>
+        <v>1900.0</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>237</v>
@@ -10641,7 +10648,7 @@
         <v>26</v>
       </c>
       <c r="D330" s="2">
-        <v>0.0</v>
+        <v>2300.0</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>237</v>
@@ -10670,7 +10677,7 @@
         <v>11</v>
       </c>
       <c r="D331" s="2">
-        <v>0.0</v>
+        <v>180.0</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>237</v>
@@ -10699,7 +10706,7 @@
         <v>17</v>
       </c>
       <c r="D332" s="2">
-        <v>0.0</v>
+        <v>270.0</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>237</v>
@@ -10728,7 +10735,7 @@
         <v>18</v>
       </c>
       <c r="D333" s="2">
-        <v>0.0</v>
+        <v>700.0</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>237</v>
@@ -10757,7 +10764,7 @@
         <v>19</v>
       </c>
       <c r="D334" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>237</v>
@@ -10786,7 +10793,7 @@
         <v>22</v>
       </c>
       <c r="D335" s="2">
-        <v>0.0</v>
+        <v>450.0</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>242</v>
@@ -10815,7 +10822,7 @@
         <v>23</v>
       </c>
       <c r="D336" s="2">
-        <v>0.0</v>
+        <v>1000.0</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>242</v>
@@ -10844,7 +10851,7 @@
         <v>24</v>
       </c>
       <c r="D337" s="2">
-        <v>0.0</v>
+        <v>1800.0</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>242</v>
@@ -10873,7 +10880,7 @@
         <v>25</v>
       </c>
       <c r="D338" s="2">
-        <v>0.0</v>
+        <v>2800.0</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>242</v>
@@ -10902,7 +10909,7 @@
         <v>26</v>
       </c>
       <c r="D339" s="2">
-        <v>0.0</v>
+        <v>4000.0</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>242</v>
@@ -10931,7 +10938,7 @@
         <v>11</v>
       </c>
       <c r="D340" s="2">
-        <v>0.0</v>
+        <v>230.0</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>242</v>
@@ -10960,7 +10967,7 @@
         <v>17</v>
       </c>
       <c r="D341" s="2">
-        <v>0.0</v>
+        <v>400.0</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>242</v>
@@ -10989,7 +10996,7 @@
         <v>18</v>
       </c>
       <c r="D342" s="2">
-        <v>0.0</v>
+        <v>950.0</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>242</v>
@@ -11018,7 +11025,7 @@
         <v>19</v>
       </c>
       <c r="D343" s="2">
-        <v>0.0</v>
+        <v>1950.0</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>242</v>
@@ -11047,7 +11054,7 @@
         <v>22</v>
       </c>
       <c r="D344" s="2">
-        <v>0.0</v>
+        <v>380.0</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>248</v>
@@ -11076,7 +11083,7 @@
         <v>23</v>
       </c>
       <c r="D345" s="2">
-        <v>0.0</v>
+        <v>900.0</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>248</v>
@@ -11105,7 +11112,7 @@
         <v>24</v>
       </c>
       <c r="D346" s="2">
-        <v>0.0</v>
+        <v>1600.0</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>248</v>
@@ -11134,7 +11141,7 @@
         <v>25</v>
       </c>
       <c r="D347" s="2">
-        <v>0.0</v>
+        <v>1900.0</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>248</v>
@@ -11163,7 +11170,7 @@
         <v>26</v>
       </c>
       <c r="D348" s="2">
-        <v>0.0</v>
+        <v>2800.0</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>248</v>
@@ -11192,7 +11199,7 @@
         <v>11</v>
       </c>
       <c r="D349" s="2">
-        <v>0.0</v>
+        <v>220.0</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>248</v>
@@ -11221,7 +11228,7 @@
         <v>17</v>
       </c>
       <c r="D350" s="2">
-        <v>0.0</v>
+        <v>400.0</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>248</v>
@@ -11250,7 +11257,7 @@
         <v>18</v>
       </c>
       <c r="D351" s="2">
-        <v>0.0</v>
+        <v>780.0</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>248</v>
@@ -11279,7 +11286,7 @@
         <v>19</v>
       </c>
       <c r="D352" s="2">
-        <v>0.0</v>
+        <v>1550.0</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>248</v>
@@ -11308,7 +11315,7 @@
         <v>22</v>
       </c>
       <c r="D353" s="2">
-        <v>0.0</v>
+        <v>370.0</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>254</v>
@@ -11337,7 +11344,7 @@
         <v>23</v>
       </c>
       <c r="D354" s="2">
-        <v>0.0</v>
+        <v>850.0</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>254</v>
@@ -11366,7 +11373,7 @@
         <v>24</v>
       </c>
       <c r="D355" s="2">
-        <v>0.0</v>
+        <v>1600.0</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>254</v>
@@ -11395,7 +11402,7 @@
         <v>25</v>
       </c>
       <c r="D356" s="2">
-        <v>0.0</v>
+        <v>3000.0</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>254</v>
@@ -11424,7 +11431,7 @@
         <v>26</v>
       </c>
       <c r="D357" s="2">
-        <v>0.0</v>
+        <v>4500.0</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>254</v>
@@ -11453,7 +11460,7 @@
         <v>11</v>
       </c>
       <c r="D358" s="2">
-        <v>0.0</v>
+        <v>220.0</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>254</v>
@@ -11482,7 +11489,7 @@
         <v>17</v>
       </c>
       <c r="D359" s="2">
-        <v>0.0</v>
+        <v>350.0</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>254</v>
@@ -11511,7 +11518,7 @@
         <v>18</v>
       </c>
       <c r="D360" s="2">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>254</v>
@@ -11540,7 +11547,7 @@
         <v>19</v>
       </c>
       <c r="D361" s="2">
-        <v>0.0</v>
+        <v>1500.0</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>254</v>
@@ -11569,7 +11576,7 @@
         <v>22</v>
       </c>
       <c r="D362" s="2">
-        <v>0.0</v>
+        <v>300.0</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>260</v>
@@ -11598,7 +11605,7 @@
         <v>23</v>
       </c>
       <c r="D363" s="2">
-        <v>0.0</v>
+        <v>720.0</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>260</v>
@@ -11627,7 +11634,7 @@
         <v>24</v>
       </c>
       <c r="D364" s="2">
-        <v>0.0</v>
+        <v>1350.0</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>260</v>
@@ -11656,7 +11663,7 @@
         <v>25</v>
       </c>
       <c r="D365" s="2">
-        <v>0.0</v>
+        <v>1700.0</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>260</v>
@@ -11685,7 +11692,7 @@
         <v>26</v>
       </c>
       <c r="D366" s="2">
-        <v>0.0</v>
+        <v>2500.0</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>260</v>
@@ -11714,7 +11721,7 @@
         <v>11</v>
       </c>
       <c r="D367" s="2">
-        <v>0.0</v>
+        <v>180.0</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>260</v>
@@ -11743,7 +11750,7 @@
         <v>17</v>
       </c>
       <c r="D368" s="2">
-        <v>0.0</v>
+        <v>270.0</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>260</v>
@@ -11772,7 +11779,7 @@
         <v>18</v>
       </c>
       <c r="D369" s="2">
-        <v>0.0</v>
+        <v>670.0</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>260</v>
@@ -11801,7 +11808,7 @@
         <v>19</v>
       </c>
       <c r="D370" s="2">
-        <v>0.0</v>
+        <v>1250.0</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>260</v>
